--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -1407,7 +1407,7 @@
         <v>131314802</v>
       </c>
       <c r="B8" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131314805</v>
       </c>
       <c r="B9" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131314711</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>131314708</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>131314712</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131314709</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131314713</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314800</v>
+        <v>131314710</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,31 +2952,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497562</v>
+        <v>497642</v>
       </c>
       <c r="R20" t="n">
-        <v>6980376</v>
+        <v>6980349</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3024,7 +3019,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3033,6 +3028,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3071,7 +3067,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314799</v>
+        <v>131314800</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -3104,7 +3100,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3114,10 +3110,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497565</v>
+        <v>497562</v>
       </c>
       <c r="R21" t="n">
-        <v>6980371</v>
+        <v>6980376</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3154,7 +3150,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,14 +3177,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3206,10 +3197,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314710</v>
+        <v>131314799</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,26 +3208,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3244,10 +3240,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497642</v>
+        <v>497565</v>
       </c>
       <c r="R22" t="n">
-        <v>6980349</v>
+        <v>6980371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3284,7 +3280,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3293,7 +3289,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3312,9 +3307,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3600,7 +3600,7 @@
         <v>131314840</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -1277,7 +1277,7 @@
         <v>131314796</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>131314802</v>
       </c>
       <c r="B8" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131314805</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131314711</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>131314708</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>131314712</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131314699</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131314709</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131314795</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>131314696</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>131314700</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>131314797</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131314713</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314710</v>
+        <v>131314800</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,26 +2952,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497642</v>
+        <v>497562</v>
       </c>
       <c r="R20" t="n">
-        <v>6980349</v>
+        <v>6980376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3019,7 +3024,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3028,7 +3033,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3067,10 +3071,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314800</v>
+        <v>131314799</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3104,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3110,10 +3114,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497562</v>
+        <v>497565</v>
       </c>
       <c r="R21" t="n">
-        <v>6980376</v>
+        <v>6980371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3150,7 +3154,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3177,9 +3181,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3197,10 +3206,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314799</v>
+        <v>131314710</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3208,31 +3217,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3240,10 +3244,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497565</v>
+        <v>497642</v>
       </c>
       <c r="R22" t="n">
-        <v>6980371</v>
+        <v>6980349</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3280,7 +3284,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,6 +3293,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3307,14 +3312,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
         <v>131314772</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131314798</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>131314840</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>131314771</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -1277,7 +1277,7 @@
         <v>131314796</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>131314802</v>
       </c>
       <c r="B8" t="n">
-        <v>79005</v>
+        <v>79006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131314805</v>
       </c>
       <c r="B9" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131314711</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>131314708</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>131314712</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131314699</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131314709</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131314795</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>131314696</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>131314700</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>131314797</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131314713</v>
       </c>
       <c r="B19" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314800</v>
+        <v>131314710</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,31 +2952,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497562</v>
+        <v>497642</v>
       </c>
       <c r="R20" t="n">
-        <v>6980376</v>
+        <v>6980349</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3024,7 +3019,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3033,6 +3028,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3071,10 +3067,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314799</v>
+        <v>131314800</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3104,7 +3100,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3114,10 +3110,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497565</v>
+        <v>497562</v>
       </c>
       <c r="R21" t="n">
-        <v>6980371</v>
+        <v>6980376</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3154,7 +3150,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,14 +3177,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3206,10 +3197,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314710</v>
+        <v>131314799</v>
       </c>
       <c r="B22" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,26 +3208,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3244,10 +3240,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497642</v>
+        <v>497565</v>
       </c>
       <c r="R22" t="n">
-        <v>6980349</v>
+        <v>6980371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3284,7 +3280,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3293,7 +3289,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3312,9 +3307,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
         <v>131314772</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131314798</v>
       </c>
       <c r="B24" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>131314840</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>131314771</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -1277,7 +1277,7 @@
         <v>131314796</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>131314802</v>
       </c>
       <c r="B8" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131314805</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131314711</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>131314708</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>131314712</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131314699</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131314709</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131314795</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>131314696</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>131314700</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>131314797</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131314713</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314710</v>
+        <v>131314800</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,26 +2952,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497642</v>
+        <v>497562</v>
       </c>
       <c r="R20" t="n">
-        <v>6980349</v>
+        <v>6980376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3019,7 +3024,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3028,7 +3033,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3067,10 +3071,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314800</v>
+        <v>131314799</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3104,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3110,10 +3114,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497562</v>
+        <v>497565</v>
       </c>
       <c r="R21" t="n">
-        <v>6980376</v>
+        <v>6980371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3150,7 +3154,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3177,9 +3181,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3197,10 +3206,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314799</v>
+        <v>131314710</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3208,31 +3217,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3240,10 +3244,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497565</v>
+        <v>497642</v>
       </c>
       <c r="R22" t="n">
-        <v>6980371</v>
+        <v>6980349</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3280,7 +3284,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,6 +3293,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3307,14 +3312,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
         <v>131314772</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131314798</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>131314840</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>131314771</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -1277,7 +1277,7 @@
         <v>131314796</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>131314802</v>
       </c>
       <c r="B8" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131314805</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131314711</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>131314708</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>131314712</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131314699</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131314709</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314795</v>
+        <v>131314696</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497547</v>
+        <v>497570</v>
       </c>
       <c r="R15" t="n">
-        <v>6980312</v>
+        <v>6980217</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,9 +2395,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2415,10 +2420,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314696</v>
+        <v>131314795</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2458,10 +2463,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497570</v>
+        <v>497547</v>
       </c>
       <c r="R16" t="n">
-        <v>6980217</v>
+        <v>6980312</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2498,7 +2503,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,14 +2530,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2553,7 +2553,7 @@
         <v>131314700</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>131314797</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131314713</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314800</v>
+        <v>131314710</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,31 +2952,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497562</v>
+        <v>497642</v>
       </c>
       <c r="R20" t="n">
-        <v>6980376</v>
+        <v>6980349</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3024,7 +3019,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3033,6 +3028,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3071,10 +3067,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314799</v>
+        <v>131314800</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3104,7 +3100,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3114,10 +3110,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497565</v>
+        <v>497562</v>
       </c>
       <c r="R21" t="n">
-        <v>6980371</v>
+        <v>6980376</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3154,7 +3150,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,14 +3177,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3206,10 +3197,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314710</v>
+        <v>131314799</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,26 +3208,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3244,10 +3240,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497642</v>
+        <v>497565</v>
       </c>
       <c r="R22" t="n">
-        <v>6980349</v>
+        <v>6980371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3284,7 +3280,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3293,7 +3289,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3312,9 +3307,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
         <v>131314772</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131314798</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>131314840</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>131314771</v>
       </c>
       <c r="B26" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -1277,7 +1277,7 @@
         <v>131314796</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>131314802</v>
       </c>
       <c r="B8" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131314805</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131314711</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>131314708</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>131314712</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131314699</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131314709</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314696</v>
+        <v>131314795</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497570</v>
+        <v>497547</v>
       </c>
       <c r="R15" t="n">
-        <v>6980217</v>
+        <v>6980312</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,14 +2395,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2420,10 +2415,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314795</v>
+        <v>131314696</v>
       </c>
       <c r="B16" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2463,10 +2458,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497547</v>
+        <v>497570</v>
       </c>
       <c r="R16" t="n">
-        <v>6980312</v>
+        <v>6980217</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2503,7 +2498,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2530,9 +2525,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2553,7 +2553,7 @@
         <v>131314700</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>131314797</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131314713</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>131314710</v>
       </c>
       <c r="B20" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>131314800</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>131314799</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>131314772</v>
       </c>
       <c r="B23" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131314798</v>
       </c>
       <c r="B24" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>131314840</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>131314771</v>
       </c>
       <c r="B26" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -1277,7 +1277,7 @@
         <v>131314796</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>131314802</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79017</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131314805</v>
       </c>
       <c r="B9" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131314711</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>131314708</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>131314712</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131314699</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131314709</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131314795</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>131314696</v>
       </c>
       <c r="B16" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>131314700</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>131314797</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131314713</v>
       </c>
       <c r="B19" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>131314710</v>
       </c>
       <c r="B20" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>131314800</v>
       </c>
       <c r="B21" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>131314799</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>131314772</v>
       </c>
       <c r="B23" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131314798</v>
       </c>
       <c r="B24" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>131314840</v>
       </c>
       <c r="B25" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>131314771</v>
       </c>
       <c r="B26" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -2941,10 +2941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314710</v>
+        <v>131314800</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,26 +2952,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497642</v>
+        <v>497562</v>
       </c>
       <c r="R20" t="n">
-        <v>6980349</v>
+        <v>6980376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3019,7 +3024,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3028,7 +3033,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3067,7 +3071,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314800</v>
+        <v>131314799</v>
       </c>
       <c r="B21" t="n">
         <v>57898</v>
@@ -3100,7 +3104,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3110,10 +3114,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497562</v>
+        <v>497565</v>
       </c>
       <c r="R21" t="n">
-        <v>6980376</v>
+        <v>6980371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3150,7 +3154,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3177,9 +3181,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3197,10 +3206,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314799</v>
+        <v>131314710</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3208,31 +3217,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3240,10 +3244,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497565</v>
+        <v>497642</v>
       </c>
       <c r="R22" t="n">
-        <v>6980371</v>
+        <v>6980349</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3280,7 +3284,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,6 +3293,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3307,14 +3312,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -1277,7 +1277,7 @@
         <v>131314796</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>131314802</v>
       </c>
       <c r="B8" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131314805</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131314711</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>131314708</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>131314712</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131314699</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131314709</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131314795</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>131314696</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>131314700</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>131314797</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131314713</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314800</v>
+        <v>131314710</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,31 +2952,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497562</v>
+        <v>497642</v>
       </c>
       <c r="R20" t="n">
-        <v>6980376</v>
+        <v>6980349</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3024,7 +3019,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3033,6 +3028,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3071,10 +3067,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314799</v>
+        <v>131314800</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3104,7 +3100,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3114,10 +3110,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497565</v>
+        <v>497562</v>
       </c>
       <c r="R21" t="n">
-        <v>6980371</v>
+        <v>6980376</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3154,7 +3150,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,14 +3177,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3206,10 +3197,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314710</v>
+        <v>131314799</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,26 +3208,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3244,10 +3240,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497642</v>
+        <v>497565</v>
       </c>
       <c r="R22" t="n">
-        <v>6980349</v>
+        <v>6980371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3284,7 +3280,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3293,7 +3289,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3312,9 +3307,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
         <v>131314772</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131314798</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>131314840</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>131314771</v>
       </c>
       <c r="B26" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -1277,7 +1277,7 @@
         <v>131314796</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>131314802</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131314805</v>
       </c>
       <c r="B9" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131314711</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>131314708</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>131314712</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131314699</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131314709</v>
       </c>
       <c r="B14" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131314795</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>131314696</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>131314700</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>131314797</v>
       </c>
       <c r="B18" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131314713</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>131314710</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>131314800</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>131314799</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>131314772</v>
       </c>
       <c r="B23" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131314798</v>
       </c>
       <c r="B24" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>131314840</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>131314771</v>
       </c>
       <c r="B26" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -2941,10 +2941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314710</v>
+        <v>131314800</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,26 +2952,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497642</v>
+        <v>497562</v>
       </c>
       <c r="R20" t="n">
-        <v>6980349</v>
+        <v>6980376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3019,7 +3024,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3028,7 +3033,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3067,7 +3071,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314800</v>
+        <v>131314799</v>
       </c>
       <c r="B21" t="n">
         <v>57902</v>
@@ -3100,7 +3104,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3110,10 +3114,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497562</v>
+        <v>497565</v>
       </c>
       <c r="R21" t="n">
-        <v>6980376</v>
+        <v>6980371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3150,7 +3154,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3177,9 +3181,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3197,10 +3206,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314799</v>
+        <v>131314710</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3208,31 +3217,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3240,10 +3244,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497565</v>
+        <v>497642</v>
       </c>
       <c r="R22" t="n">
-        <v>6980371</v>
+        <v>6980349</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3280,7 +3284,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,6 +3293,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3307,14 +3312,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -2941,10 +2941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314800</v>
+        <v>131314710</v>
       </c>
       <c r="B20" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,31 +2952,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2984,10 +2979,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497562</v>
+        <v>497642</v>
       </c>
       <c r="R20" t="n">
-        <v>6980376</v>
+        <v>6980349</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3024,7 +3019,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3033,6 +3028,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3071,7 +3067,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314799</v>
+        <v>131314800</v>
       </c>
       <c r="B21" t="n">
         <v>57902</v>
@@ -3104,7 +3100,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3114,10 +3110,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497565</v>
+        <v>497562</v>
       </c>
       <c r="R21" t="n">
-        <v>6980371</v>
+        <v>6980376</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3154,7 +3150,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3181,14 +3177,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3206,10 +3197,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314710</v>
+        <v>131314799</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,26 +3208,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3244,10 +3240,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497642</v>
+        <v>497565</v>
       </c>
       <c r="R22" t="n">
-        <v>6980349</v>
+        <v>6980371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3284,7 +3280,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3293,7 +3289,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3312,9 +3307,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -1277,7 +1277,7 @@
         <v>131314796</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>131314802</v>
       </c>
       <c r="B8" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>131314805</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>131314711</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>131314708</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>131314712</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>131314699</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>131314709</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>131314795</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>131314696</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>131314700</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>131314797</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>131314713</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314710</v>
+        <v>131314800</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,26 +2952,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2979,10 +2984,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497642</v>
+        <v>497562</v>
       </c>
       <c r="R20" t="n">
-        <v>6980349</v>
+        <v>6980376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3019,7 +3024,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3028,7 +3033,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3067,10 +3071,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314800</v>
+        <v>131314799</v>
       </c>
       <c r="B21" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3104,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3110,10 +3114,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497562</v>
+        <v>497565</v>
       </c>
       <c r="R21" t="n">
-        <v>6980376</v>
+        <v>6980371</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3150,7 +3154,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3177,9 +3181,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3197,10 +3206,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314799</v>
+        <v>131314710</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3208,31 +3217,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3240,10 +3244,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497565</v>
+        <v>497642</v>
       </c>
       <c r="R22" t="n">
-        <v>6980371</v>
+        <v>6980349</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3280,7 +3284,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,6 +3293,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3307,14 +3312,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3335,7 +3335,7 @@
         <v>131314772</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>131314798</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>131314840</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>131314771</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17084274</v>
+        <v>17084276</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497591.1528811002</v>
+        <v>497672</v>
       </c>
       <c r="R2" t="n">
-        <v>6979684.1275644</v>
+        <v>6979473</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,21 +752,11 @@
           <t>2014-09-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -783,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>120-årig talldominerad skog av ristyp</t>
+          <t>120-årig granskog av lågörtstyp med ris</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr"/>
@@ -806,53 +791,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>58434994</v>
+        <v>17084274</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Våge, ca 300 m väster - nordväst om, ca 200 m öster om Smalvågens nordligas, Jmt</t>
+          <t>Våge, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497663.9674703681</v>
+        <v>497591</v>
       </c>
       <c r="R3" t="n">
-        <v>6979515.642605682</v>
+        <v>6979684</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,27 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest grandominerad</t>
+          <t>2014-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,65 +882,73 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>120-årig talldominerad skog av ristyp</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för kalktallskogar</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>58434996</v>
+        <v>131314708</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Våge, ca 300 m väster - nordväst om, ca 200 m öster om Smalvågens nordligas, Jmt</t>
+          <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497599.6977908127</v>
+        <v>497662</v>
       </c>
       <c r="R4" t="n">
-        <v>6979526.1595767</v>
+        <v>6980257</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,27 +975,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest grandominerad</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,68 +994,87 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58434997</v>
+        <v>131314709</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Våge, ca 300 m väster - nordväst om, ca 200 m öster om Smalvågens nordligas, Jmt</t>
+          <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497650.7574550838</v>
+        <v>497652</v>
       </c>
       <c r="R5" t="n">
-        <v>6979529.764290893</v>
+        <v>6980293</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,27 +1101,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, mest grandominerad</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,68 +1115,92 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>58434999</v>
+        <v>131314710</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Våge, ca 300 m väster - nordväst om, ca 200 m öster om Smalvågens nordligas, Jmt</t>
+          <t>Rensved NV, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497613.4017379469</v>
+        <v>497642</v>
       </c>
       <c r="R6" t="n">
-        <v>6979564.388795042</v>
+        <v>6980349</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,27 +1227,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, mest grandominerad</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,60 +1246,76 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131314796</v>
+        <v>131314711</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1317,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497551</v>
+        <v>497604</v>
       </c>
       <c r="R7" t="n">
-        <v>6980337</v>
+        <v>6980360</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,7 +1363,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,6 +1372,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1404,32 +1411,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131314802</v>
+        <v>131314712</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1442,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497562</v>
+        <v>497629</v>
       </c>
       <c r="R8" t="n">
-        <v>6980264</v>
+        <v>6980392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,6 +1487,11 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1497,17 +1509,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1525,37 +1537,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131314805</v>
+        <v>131314713</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1563,10 +1575,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497523</v>
+        <v>497613</v>
       </c>
       <c r="R9" t="n">
-        <v>6980392</v>
+        <v>6980422</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1599,6 +1611,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,14 +1663,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131314711</v>
+        <v>131314840</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1684,10 +1701,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497604</v>
+        <v>497586</v>
       </c>
       <c r="R10" t="n">
-        <v>6980360</v>
+        <v>6980364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,11 +1737,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131314708</v>
+        <v>131314802</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,21 +1795,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1810,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497662</v>
+        <v>497562</v>
       </c>
       <c r="R11" t="n">
-        <v>6980257</v>
+        <v>6980264</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,11 +1860,6 @@
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1865,22 +1872,22 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1898,10 +1905,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131314712</v>
+        <v>131314696</v>
       </c>
       <c r="B12" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,26 +1916,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1936,10 +1948,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497629</v>
+        <v>497570</v>
       </c>
       <c r="R12" t="n">
-        <v>6980392</v>
+        <v>6980217</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1976,7 +1988,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,7 +1997,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2004,9 +2015,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2027,7 +2043,7 @@
         <v>131314699</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2159,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131314709</v>
+        <v>131314700</v>
       </c>
       <c r="B14" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2170,26 +2186,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2197,10 +2218,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497652</v>
+        <v>497592</v>
       </c>
       <c r="R14" t="n">
-        <v>6980293</v>
+        <v>6980431</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2235,13 +2256,17 @@
           <t>2026-02-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2250,24 +2275,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2285,10 +2310,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131314795</v>
+        <v>131314770</v>
       </c>
       <c r="B15" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,10 +2353,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>497547</v>
+        <v>497560</v>
       </c>
       <c r="R15" t="n">
-        <v>6980312</v>
+        <v>6980219</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2395,9 +2420,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2415,10 +2445,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131314696</v>
+        <v>131314771</v>
       </c>
       <c r="B16" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2458,10 +2488,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>497570</v>
+        <v>497557</v>
       </c>
       <c r="R16" t="n">
-        <v>6980217</v>
+        <v>6980240</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2498,7 +2528,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,14 +2555,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2550,10 +2575,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131314700</v>
+        <v>131314772</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2583,7 +2608,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2593,10 +2618,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497592</v>
+        <v>497715</v>
       </c>
       <c r="R17" t="n">
-        <v>6980431</v>
+        <v>6980084</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2633,7 +2658,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en tall.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2652,22 +2677,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2685,10 +2705,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131314797</v>
+        <v>131314795</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2718,7 +2738,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2728,10 +2748,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497546</v>
+        <v>497547</v>
       </c>
       <c r="R18" t="n">
-        <v>6980329</v>
+        <v>6980312</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2768,7 +2788,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2815,10 +2835,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131314713</v>
+        <v>131314796</v>
       </c>
       <c r="B19" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2826,26 +2846,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2853,10 +2878,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497613</v>
+        <v>497551</v>
       </c>
       <c r="R19" t="n">
-        <v>6980422</v>
+        <v>6980337</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2893,7 +2918,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på en gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2902,7 +2927,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2941,10 +2965,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131314800</v>
+        <v>131314797</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2984,10 +3008,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497562</v>
+        <v>497546</v>
       </c>
       <c r="R20" t="n">
-        <v>6980376</v>
+        <v>6980329</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3071,10 +3095,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131314799</v>
+        <v>131314798</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3104,7 +3128,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3114,10 +3138,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497565</v>
+        <v>497540</v>
       </c>
       <c r="R21" t="n">
-        <v>6980371</v>
+        <v>6980397</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3154,7 +3178,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Äldre bohål i grantickerötad högstubbe av gran. På ca 1 meters höjd över marken och ca 45 - 50 mm i diameter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3183,12 +3207,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3206,10 +3230,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131314710</v>
+        <v>131314799</v>
       </c>
       <c r="B22" t="n">
-        <v>79266</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,26 +3241,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3244,10 +3273,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>497642</v>
+        <v>497565</v>
       </c>
       <c r="R22" t="n">
-        <v>6980349</v>
+        <v>6980371</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3284,7 +3313,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3293,7 +3322,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3312,9 +3340,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3332,10 +3365,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131314772</v>
+        <v>131314800</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3365,7 +3398,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3375,10 +3408,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497715</v>
+        <v>497562</v>
       </c>
       <c r="R23" t="n">
-        <v>6980084</v>
+        <v>6980376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3415,7 +3448,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3462,53 +3495,56 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131314798</v>
+        <v>14984598</v>
       </c>
       <c r="B24" t="n">
-        <v>57904</v>
+        <v>43249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>101248</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rensved NV, Jmt</t>
+          <t>Väg 568, mellan Börön och ca 700 m NV om Våge,, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497540</v>
+        <v>497560</v>
       </c>
       <c r="R24" t="n">
-        <v>6980397</v>
+        <v>6979533</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3535,17 +3571,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2009-06-28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2009-06-28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre bohål i grantickerötad högstubbe av gran. På ca 1 meters höjd över marken och ca 45 - 50 mm i diameter.</t>
+          <t>ca 50 m Ö om Smalvågens Nspets, 1 ex., Hane. På daggkåpsblad i fuktig miljö, vatten i vägdike. Ormrot inom 30 m.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3557,88 +3593,69 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Vägkant, fuktig källpåverkad mark, vatten i dike, brudsporre</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131314840</v>
+        <v>58434992</v>
       </c>
       <c r="B25" t="n">
-        <v>79266</v>
+        <v>101326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rensved NV, Jmt</t>
+          <t>Våge, ca 300 m väster - nordväst om, ca 200 m öster om Smalvågens nordligas, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>497586</v>
+        <v>497671</v>
       </c>
       <c r="R25" t="n">
-        <v>6980364</v>
+        <v>6979491</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3665,12 +3682,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2010-07-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2010-07-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest grandominerad</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3679,92 +3701,63 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Bengt Petterson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131314771</v>
+        <v>58434994</v>
       </c>
       <c r="B26" t="n">
-        <v>57904</v>
+        <v>101326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rensved NV, Jmt</t>
+          <t>Våge, ca 300 m väster - nordväst om, ca 200 m öster om Smalvågens nordligas, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>497557</v>
+        <v>497664</v>
       </c>
       <c r="R26" t="n">
-        <v>6980240</v>
+        <v>6979516</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3791,17 +3784,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2010-07-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2010-07-15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Kalkbarrskog, mest grandominerad</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3812,39 +3805,441 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Bengt Petterson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>58434996</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Våge, ca 300 m väster - nordväst om, ca 200 m öster om Smalvågens nordligas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>497600</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6979526</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2010-07-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2010-07-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest grandominerad</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>58434997</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Våge, ca 300 m väster - nordväst om, ca 200 m öster om Smalvågens nordligas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>497651</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6979530</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2010-07-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2010-07-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest grandominerad</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>58434999</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Våge, ca 300 m väster - nordväst om, ca 200 m öster om Smalvågens nordligas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>497613</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6979564</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2010-07-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2010-07-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, mest grandominerad</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>17084275</v>
+      </c>
+      <c r="B30" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Våge, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>497670</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6979494</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2014-09-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2014-09-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>120-årig granskog av lågörtstyp med ris</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för kalktallskogar</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60614-2022 artfynd.xlsx
+++ b/artfynd/A 60614-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17084276</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Åtgärdsprogram för kalktallskogar</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17084274</t>
         </is>
       </c>
     </row>
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314708</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314709</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,6 +1307,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314710</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1408,6 +1438,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314711</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1534,6 +1569,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314712</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1660,6 +1700,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314713</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1781,6 +1826,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314840</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1902,6 +1952,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314802</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2037,6 +2092,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314696</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2172,6 +2232,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314699</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2307,6 +2372,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314700</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2442,6 +2512,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314770</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2572,6 +2647,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314771</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2702,6 +2782,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314772</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2832,6 +2917,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314795</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2962,6 +3052,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314796</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3092,6 +3187,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314797</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3227,6 +3327,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314798</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3362,6 +3467,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314799</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3492,6 +3602,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131314800</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3614,6 +3729,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14984598</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3716,6 +3836,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58434992</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3818,6 +3943,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58434994</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3920,6 +4050,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58434996</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4022,6 +4157,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58434997</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4124,6 +4264,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58434999</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4240,8 +4385,44 @@
           <t>Åtgärdsprogram för kalktallskogar</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17084275</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>